--- a/etl/sources/Sports_Framework_v14.xlsx
+++ b/etl/sources/Sports_Framework_v14.xlsx
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B4" s="190" t="inlineStr">
         <is>
-          <t>Foot (run / hike / nav)</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="C4" s="190" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="D6" s="190" t="inlineStr">
         <is>
-          <t>Cycling disciplines on technical trail / mountain surfaces (mountain biking). Gravel folds in once D-006 splits.</t>
+          <t>Cycling disciplines on technical trail / mountain surfaces (mountain biking, gravel, cross-country).</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="B7" s="190" t="inlineStr">
         <is>
-          <t>Snow travel (foot)</t>
+          <t>Snow Travel (on foot)</t>
         </is>
       </c>
       <c r="C7" s="190" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="B8" s="190" t="inlineStr">
         <is>
-          <t>Snow travel (gliding)</t>
+          <t>Skiing</t>
         </is>
       </c>
       <c r="C8" s="190" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="B9" s="190" t="inlineStr">
         <is>
-          <t>Climbing (rope-protected)</t>
+          <t>Roped climbing</t>
         </is>
       </c>
       <c r="C9" s="190" t="inlineStr">
@@ -6263,85 +6263,85 @@
       <c r="C27" s="190" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="190" t="inlineStr">
         <is>
           <t>D-030</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="190" t="inlineStr">
         <is>
           <t>bike_pavement</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="190" t="inlineStr">
         <is>
           <t>Gravel cycling pools with road training</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="190" t="inlineStr">
         <is>
           <t>D-030</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="190" t="inlineStr">
         <is>
           <t>bike_offroad</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="190" t="inlineStr">
         <is>
           <t>Gravel cycling also pools with off-road training</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="190" t="inlineStr">
         <is>
           <t>D-031</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="190" t="inlineStr">
         <is>
           <t>bike_offroad</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="190" t="inlineStr">
         <is>
           <t>Cross country (XC) mountain biking</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="190" t="inlineStr">
         <is>
           <t>D-032</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="190" t="inlineStr">
         <is>
           <t>paddle_flatwater</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="190" t="inlineStr">
         <is>
           <t>Stand-up paddleboard, flatwater modality</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="190" t="inlineStr">
         <is>
           <t>D-019</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="190" t="inlineStr">
         <is>
           <t>paddle_whitewater</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="190" t="inlineStr">
         <is>
           <t>Paddle rafting on moving/whitewater</t>
         </is>
@@ -8881,201 +8881,201 @@
       </c>
     </row>
     <row r="31" ht="139.5" customHeight="1" s="191">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="190" t="inlineStr">
         <is>
           <t>D-030</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="190" t="inlineStr">
         <is>
           <t>Gravel Cycling</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="190" t="inlineStr">
         <is>
           <t>Cycling</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="190" t="inlineStr">
         <is>
           <t>Long Distance / Endurance Cycling · Adventure Racing</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="190" t="inlineStr">
         <is>
           <t>Same as Road Cycling (D-006): 2–3 weeks Zone 2 before structured intervals. Add loose-surface bike handling at low tire pressure.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="190" t="inlineStr">
         <is>
           <t>Same structure as Road Cycling (D-006). Gravel-specific: sustained tempo on mixed surface; loose-surface handling and longer unsupported efforts in Build.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="190" t="inlineStr">
         <is>
           <t>Same as Road Cycling (D-006): 10–15%/week ride hours; FTP intervals +1 rep or +5% duration per 2-week block, not both.</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="190" t="inlineStr">
         <is>
           <t>Same as Road Cycling (D-006) by age group; watch patellar tendon.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="190" t="inlineStr">
         <is>
           <t>1–2 weeks. Volume cut 40–50%. Maintain 2 shorter intensity sessions.</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="190" t="inlineStr">
         <is>
           <t>Knee pain (patellar tendon, IT band) · Lower back (aero position) · Hand/wrist fatigue from sustained surface vibration</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="190" t="inlineStr">
         <is>
           <t>Rapid intensity escalation without aerobic base · Poor saddle height · Poor cleat alignment</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="190" t="inlineStr">
         <is>
           <t>Same as Road Cycling (D-006): active recovery spin, hip flexor stretch, sleep.</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="190" t="inlineStr">
         <is>
           <t>Gravel-specific: extrapolated from road cycling literature (Strong for the shared road-cycling claims).</t>
         </is>
       </c>
     </row>
     <row r="32" ht="139.5" customHeight="1" s="191">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="190" t="inlineStr">
         <is>
           <t>D-031</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="190" t="inlineStr">
         <is>
           <t>Cross Country Cycling</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="190" t="inlineStr">
         <is>
           <t>Cycling</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="190" t="inlineStr">
         <is>
           <t>Long Distance / Endurance Cycling · Adventure Racing · XC MTB</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="190" t="inlineStr">
         <is>
           <t>Same as Mountain Biking (D-008): 4–6 weeks road/easy-trail aerobic base and pedaling mechanics before technical XC riding.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="190" t="inlineStr">
         <is>
           <t>Same structure as Mountain Biking (D-008), XC-racing focus: aerobic base + sustained climbing power; less technical-descent emphasis than Enduro.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="190" t="inlineStr">
         <is>
           <t>Same as Mountain Biking (D-008): 10–15%/week ride hours; add one new technical element per 2-week block (not by volume).</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="190" t="inlineStr">
         <is>
           <t>Same as Mountain Biking (D-008) by age group; CNS-fatigue caps on hard technical days.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="190" t="inlineStr">
         <is>
           <t>1–2 weeks. Volume cut 35–50%. Maintain 1 technical skills session.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="190" t="inlineStr">
         <is>
           <t>Lower back pain · Knee pain (fit) · Hand/wrist numbness · Shoulder impingement · Crashes</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="190" t="inlineStr">
         <is>
           <t>Skipping road base phase · Riding technically while fatigued · Poor bike fit · Insufficient core strength</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="190" t="inlineStr">
         <is>
           <t>Same as Mountain Biking (D-008): thoracic/lat foam roll, sleep, hip flexor stretch.</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="190" t="inlineStr">
         <is>
           <t>XC-specific: shares Mountain Biking evidence base (practitioner consensus for skill/CNS).</t>
         </is>
       </c>
     </row>
     <row r="33" ht="139.5" customHeight="1" s="191">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="190" t="inlineStr">
         <is>
           <t>D-032</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="190" t="inlineStr">
         <is>
           <t>Stand-up Paddleboard</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="190" t="inlineStr">
         <is>
           <t>Water / Paddle</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="190" t="inlineStr">
         <is>
           <t>Flatwater / Touring · Adventure Racing (minor)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="190" t="inlineStr">
         <is>
           <t>Same as Kayaking (D-010): 4–6 weeks flat-water paddle technique base. SUP-specific: build standing balance and anti-rotation core before volume.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="190" t="inlineStr">
         <is>
           <t>Same structure as Kayaking (D-010): BASE flat-water technique + balance; BUILD volume; PEAK race-sim. Standing balance and core stability are the SUP-specific demand.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="190" t="inlineStr">
         <is>
           <t>Same as Kayaking (D-010): 10–15%/week paddle hours; grip sessions max 3×/week.</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="190" t="inlineStr">
         <is>
           <t>Same as Kayaking (D-010) by age group; shoulder recovery 48–72 hr for masters.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="190" t="inlineStr">
         <is>
           <t>1–2 weeks. Volume cut 40–50%.</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="190" t="inlineStr">
         <is>
           <t>Shoulder impingement / rotator cuff · Wrist tendinopathy (paddle grip) · Lower back (standing posture, anti-rotation load)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="190" t="inlineStr">
         <is>
           <t>Arm-dominant paddling · Rapid volume increase · Neglecting shoulder antagonist work · Insufficient core/balance base</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="190" t="inlineStr">
         <is>
           <t>Same as Kayaking (D-010): rotator-cuff external rotation, wrist extensor stretch, hip flexor stretch.</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="190" t="inlineStr">
         <is>
           <t>SUP-specific: extrapolated from kayak/canoe paddle-sports literature (Moderate).</t>
         </is>
@@ -15154,8 +15154,8 @@
   <mergeCells count="16">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B7:F7"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="B7:F7"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="A1:F1"/>

--- a/etl/sources/Sports_Framework_v14.xlsx
+++ b/etl/sources/Sports_Framework_v14.xlsx
@@ -19,6 +19,7 @@
     <sheet name="Discipline Training Gaps" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Modality Groups" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Discipline Modality Membership" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Craft Discipline Aliases" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -6352,6 +6353,275 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Craft Slug</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Discipline ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Group Kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>kayak</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>D-010</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>paddle</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>canoe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D-011</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>paddle</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>packraft</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D-009</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>paddle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>road_bike</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D-006</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gravel_bike</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D-006</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gravel_bike</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D-030</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>gravel_bike</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D-031</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mountain_bike</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D-008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mountain_bike</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D-031</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cycling_trainer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D-006</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cycling_trainer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D-007</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cycling_trainer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D-008</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cycling_trainer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D-030</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cycling_trainer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D-031</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -15154,8 +15424,8 @@
   <mergeCells count="16">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="A1:F1"/>
